--- a/تاريخ ترم ثاني.xlsx
+++ b/تاريخ ترم ثاني.xlsx
@@ -7478,7 +7478,7 @@
         <v>26</v>
       </c>
       <c r="K31">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
   </sheetData>
@@ -7597,7 +7597,7 @@
         <v>32</v>
       </c>
       <c r="K3">
-        <v>32</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="4">
@@ -7629,7 +7629,7 @@
         <v>15</v>
       </c>
       <c r="K4">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -7696,7 +7696,7 @@
         <v>16</v>
       </c>
       <c r="K6">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7">
@@ -7728,7 +7728,7 @@
         <v>21</v>
       </c>
       <c r="K7">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -7996,7 +7996,7 @@
         <v>19</v>
       </c>
       <c r="K15">
-        <v>26</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="16">
@@ -8028,7 +8028,7 @@
         <v>15</v>
       </c>
       <c r="K16">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -8092,7 +8092,7 @@
         <v>17</v>
       </c>
       <c r="K18">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19">
